--- a/23:24/PLteamsData23:24_with_tight_schedule.xlsx
+++ b/23:24/PLteamsData23:24_with_tight_schedule.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shlomiasraf/Desktop/degree/MomentumProject/23:24/PLteamsData23:"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AAE77AE-FF41-6946-858E-FB3104CADF3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="760" windowWidth="30000" windowHeight="17880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Arsenal" sheetId="1" r:id="rId1"/>
@@ -34,7 +28,7 @@
     <sheet name="West Ham" sheetId="19" r:id="rId19"/>
     <sheet name="Wolves" sheetId="20" r:id="rId20"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -608,15 +602,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -624,7 +618,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -676,19 +670,11 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -730,7 +716,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -762,27 +748,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -814,24 +782,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -1007,17 +957,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1049,7 +993,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1066,7 +1010,7 @@
         <v>86</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -1078,7 +1022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1095,7 +1039,7 @@
         <v>86</v>
       </c>
       <c r="F3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1110,7 +1054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1142,7 +1086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1171,10 +1115,10 @@
         <v>7</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1206,7 +1150,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1235,10 +1179,10 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1267,10 +1211,10 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1299,10 +1243,10 @@
         <v>6</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1331,10 +1275,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1366,7 +1310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1395,10 +1339,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1430,7 +1374,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1462,7 +1406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1494,7 +1438,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1526,7 +1470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1555,10 +1499,10 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1590,7 +1534,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1619,10 +1563,10 @@
         <v>5</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -1651,10 +1595,10 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1686,7 +1630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1715,10 +1659,10 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -1750,7 +1694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1782,7 +1726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -1811,10 +1755,10 @@
         <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -1846,7 +1790,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1878,7 +1822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -1907,10 +1851,10 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -1939,10 +1883,10 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -1974,7 +1918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -2003,10 +1947,10 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -2038,7 +1982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2067,10 +2011,10 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2102,7 +2046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2134,7 +2078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2166,7 +2110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2195,10 +2139,10 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2227,10 +2171,10 @@
         <v>5</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2268,11 +2212,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2304,7 +2248,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -2333,7 +2277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -2362,10 +2306,10 @@
         <v>5</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>157</v>
       </c>
@@ -2394,10 +2338,10 @@
         <v>6</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -2429,7 +2373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -2458,10 +2402,10 @@
         <v>6</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2493,7 +2437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -2525,7 +2469,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -2554,10 +2498,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2586,10 +2530,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -2618,10 +2562,10 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -2650,10 +2594,10 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2682,10 +2626,10 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>140</v>
       </c>
@@ -2714,10 +2658,10 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -2749,7 +2693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -2781,7 +2725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -2813,7 +2757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -2845,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -2874,10 +2818,10 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -2906,10 +2850,10 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2938,10 +2882,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -2970,10 +2914,10 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3005,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3037,7 +2981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -3066,10 +3010,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3098,10 +3042,10 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -3130,10 +3074,10 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -3165,7 +3109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -3194,10 +3138,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -3229,7 +3173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -3261,7 +3205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -3293,7 +3237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -3322,10 +3266,10 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -3357,7 +3301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -3389,7 +3333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -3418,10 +3362,10 @@
         <v>6</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -3450,10 +3394,10 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -3485,7 +3429,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -3514,7 +3458,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3523,11 +3467,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3559,7 +3503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -3588,7 +3532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3617,10 +3561,10 @@
         <v>7</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3652,7 +3596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3684,7 +3628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -3716,7 +3660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -3748,7 +3692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3780,7 +3724,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -3809,10 +3753,10 @@
         <v>6</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3841,10 +3785,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>179</v>
       </c>
@@ -3876,7 +3820,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -3908,7 +3852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -3940,7 +3884,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3972,7 +3916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -4004,7 +3948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>161</v>
       </c>
@@ -4036,7 +3980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4065,10 +4009,10 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -4097,10 +4041,10 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -4132,7 +4076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -4164,7 +4108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -4196,7 +4140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>100</v>
       </c>
@@ -4228,7 +4172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -4257,10 +4201,10 @@
         <v>6</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>141</v>
       </c>
@@ -4292,7 +4236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -4321,10 +4265,10 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -4356,7 +4300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -4385,10 +4329,10 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -4420,7 +4364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -4452,7 +4396,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -4481,10 +4425,10 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -4516,7 +4460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -4545,10 +4489,10 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -4580,7 +4524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -4612,7 +4556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -4644,7 +4588,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -4676,7 +4620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -4708,7 +4652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -4737,10 +4681,10 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -4778,11 +4722,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4814,7 +4758,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -4843,7 +4787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -4875,7 +4819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -4904,10 +4848,10 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4939,7 +4883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -4971,7 +4915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -5003,7 +4947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -5035,7 +4979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -5064,10 +5008,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>147</v>
       </c>
@@ -5099,7 +5043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>179</v>
       </c>
@@ -5131,7 +5075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -5163,7 +5107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -5192,10 +5136,10 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>127</v>
       </c>
@@ -5227,7 +5171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>140</v>
       </c>
@@ -5259,7 +5203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -5291,7 +5235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -5323,7 +5267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -5355,7 +5299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -5384,10 +5328,10 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -5416,10 +5360,10 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -5448,10 +5392,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>173</v>
       </c>
@@ -5480,10 +5424,10 @@
         <v>6</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -5515,7 +5459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -5547,7 +5491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -5579,7 +5523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>164</v>
       </c>
@@ -5611,7 +5555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>180</v>
       </c>
@@ -5640,10 +5584,10 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -5675,7 +5619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -5704,10 +5648,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -5736,10 +5680,10 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -5771,7 +5715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -5800,10 +5744,10 @@
         <v>6</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -5835,7 +5779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -5864,10 +5808,10 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -5899,7 +5843,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -5928,10 +5872,10 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -5963,7 +5907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -5995,7 +5939,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -6033,11 +5977,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6069,7 +6013,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -6098,7 +6042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>157</v>
       </c>
@@ -6127,10 +6071,10 @@
         <v>5</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6162,7 +6106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -6194,7 +6138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -6226,7 +6170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -6255,10 +6199,10 @@
         <v>5</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -6287,10 +6231,10 @@
         <v>5</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -6319,10 +6263,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>138</v>
       </c>
@@ -6354,7 +6298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6386,7 +6330,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -6415,10 +6359,10 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -6447,10 +6391,10 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -6482,7 +6426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -6514,7 +6458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -6546,7 +6490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -6575,10 +6519,10 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>148</v>
       </c>
@@ -6610,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -6642,7 +6586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -6671,10 +6615,10 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -6703,10 +6647,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>181</v>
       </c>
@@ -6738,7 +6682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -6767,10 +6711,10 @@
         <v>5</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>153</v>
       </c>
@@ -6802,7 +6746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -6834,7 +6778,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -6866,7 +6810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -6895,10 +6839,10 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -6930,7 +6874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -6959,10 +6903,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -6991,10 +6935,10 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -7026,7 +6970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -7058,7 +7002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -7090,7 +7034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -7122,7 +7066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -7154,7 +7098,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -7186,7 +7130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>155</v>
       </c>
@@ -7215,10 +7159,10 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -7250,7 +7194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -7288,11 +7232,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7324,7 +7268,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -7353,7 +7297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -7382,10 +7326,10 @@
         <v>7</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7414,10 +7358,10 @@
         <v>7</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -7449,7 +7393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -7481,7 +7425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -7513,7 +7457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -7542,10 +7486,10 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -7574,10 +7518,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -7606,10 +7550,10 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -7638,10 +7582,10 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -7670,10 +7614,10 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -7705,7 +7649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>160</v>
       </c>
@@ -7734,10 +7678,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -7769,7 +7713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -7798,10 +7742,10 @@
         <v>6</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -7833,7 +7777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -7865,7 +7809,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>171</v>
       </c>
@@ -7897,7 +7841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -7926,10 +7870,10 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>149</v>
       </c>
@@ -7961,7 +7905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -7993,7 +7937,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>182</v>
       </c>
@@ -8025,7 +7969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -8054,10 +7998,10 @@
         <v>5</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -8086,10 +8030,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -8121,7 +8065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -8153,7 +8097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -8182,10 +8126,10 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -8214,10 +8158,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -8249,7 +8193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -8278,10 +8222,10 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -8313,7 +8257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -8342,10 +8286,10 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -8377,7 +8321,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -8409,7 +8353,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -8441,7 +8385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -8470,10 +8414,10 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -8505,7 +8449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -8543,11 +8487,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8579,7 +8523,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -8608,7 +8552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -8637,10 +8581,10 @@
         <v>7</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>157</v>
       </c>
@@ -8669,10 +8613,10 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -8704,7 +8648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -8733,10 +8677,10 @@
         <v>7</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -8768,7 +8712,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -8800,7 +8744,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -8829,10 +8773,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -8861,10 +8805,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -8893,10 +8837,10 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -8925,10 +8869,10 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>159</v>
       </c>
@@ -8960,7 +8904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -8992,7 +8936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>128</v>
       </c>
@@ -9024,7 +8968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -9056,7 +9000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -9085,10 +9029,10 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -9120,7 +9064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -9152,7 +9096,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -9181,10 +9125,10 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -9213,10 +9157,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -9248,7 +9192,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -9280,7 +9224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -9312,7 +9256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -9341,10 +9285,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -9376,7 +9320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -9405,10 +9349,10 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -9440,7 +9384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -9472,7 +9416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -9501,10 +9445,10 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -9536,7 +9480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -9565,10 +9509,10 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -9600,7 +9544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -9629,10 +9573,10 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>174</v>
       </c>
@@ -9661,10 +9605,10 @@
         <v>5</v>
       </c>
       <c r="J35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -9696,7 +9640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>155</v>
       </c>
@@ -9725,10 +9669,10 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -9757,10 +9701,10 @@
         <v>7</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -9798,11 +9742,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9834,7 +9778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -9863,7 +9807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -9892,10 +9836,10 @@
         <v>6</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -9927,7 +9871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -9959,7 +9903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -9991,7 +9935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -10023,7 +9967,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -10052,10 +9996,10 @@
         <v>5</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -10084,10 +10028,10 @@
         <v>6</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -10116,10 +10060,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -10148,10 +10092,10 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -10180,10 +10124,10 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -10215,7 +10159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>140</v>
       </c>
@@ -10244,10 +10188,10 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -10279,7 +10223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -10311,7 +10255,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>161</v>
       </c>
@@ -10340,10 +10284,10 @@
         <v>5</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>129</v>
       </c>
@@ -10372,10 +10316,10 @@
         <v>6</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -10407,7 +10351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -10436,10 +10380,10 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -10468,10 +10412,10 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -10500,10 +10444,10 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -10535,7 +10479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -10567,7 +10511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>184</v>
       </c>
@@ -10596,10 +10540,10 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -10631,7 +10575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -10660,10 +10604,10 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>154</v>
       </c>
@@ -10695,7 +10639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -10724,10 +10668,10 @@
         <v>5</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>104</v>
       </c>
@@ -10759,7 +10703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -10788,10 +10732,10 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -10823,7 +10767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -10852,10 +10796,10 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -10887,7 +10831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -10919,7 +10863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -10948,10 +10892,10 @@
         <v>6</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -10983,7 +10927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -11015,7 +10959,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -11053,11 +10997,11 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11089,7 +11033,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -11118,7 +11062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -11150,7 +11094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -11182,7 +11126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -11211,10 +11155,10 @@
         <v>7</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -11246,7 +11190,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -11278,7 +11222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -11307,10 +11251,10 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -11342,7 +11286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>186</v>
       </c>
@@ -11371,10 +11315,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -11403,10 +11347,10 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -11435,10 +11379,10 @@
         <v>5</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -11470,7 +11414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>160</v>
       </c>
@@ -11499,10 +11443,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -11534,7 +11478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -11563,10 +11507,10 @@
         <v>6</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -11595,10 +11539,10 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -11630,7 +11574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -11662,7 +11606,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -11691,10 +11635,10 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -11723,10 +11667,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -11758,7 +11702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -11790,7 +11734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>184</v>
       </c>
@@ -11819,10 +11763,10 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -11854,7 +11798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -11883,10 +11827,10 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -11918,7 +11862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -11950,7 +11894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -11979,10 +11923,10 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -12014,7 +11958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -12046,7 +11990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -12078,7 +12022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -12107,10 +12051,10 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -12142,7 +12086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -12174,7 +12118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -12203,10 +12147,10 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>109</v>
       </c>
@@ -12235,10 +12179,10 @@
         <v>6</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -12270,7 +12214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -12308,11 +12252,11 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12344,7 +12288,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -12373,7 +12317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -12402,10 +12346,10 @@
         <v>7</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>176</v>
       </c>
@@ -12437,7 +12381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -12469,7 +12413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -12501,7 +12445,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -12533,7 +12477,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -12562,10 +12506,10 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -12594,10 +12538,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>93</v>
       </c>
@@ -12629,7 +12573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>94</v>
       </c>
@@ -12661,7 +12605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>140</v>
       </c>
@@ -12690,10 +12634,10 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -12725,7 +12669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -12757,7 +12701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -12786,10 +12730,10 @@
         <v>5</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -12818,10 +12762,10 @@
         <v>6</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -12853,7 +12797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -12885,7 +12829,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -12917,7 +12861,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>131</v>
       </c>
@@ -12946,10 +12890,10 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>181</v>
       </c>
@@ -12981,7 +12925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -13010,10 +12954,10 @@
         <v>5</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>141</v>
       </c>
@@ -13045,7 +12989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -13074,10 +13018,10 @@
         <v>6</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -13106,10 +13050,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -13138,10 +13082,10 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -13173,7 +13117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -13205,7 +13149,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -13234,10 +13178,10 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>165</v>
       </c>
@@ -13269,7 +13213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -13298,10 +13242,10 @@
         <v>5</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -13333,7 +13277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -13362,10 +13306,10 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>174</v>
       </c>
@@ -13397,7 +13341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -13429,7 +13373,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -13458,10 +13402,10 @@
         <v>5</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -13493,7 +13437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -13522,10 +13466,10 @@
         <v>5</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -13563,11 +13507,11 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13599,7 +13543,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -13628,7 +13572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -13657,10 +13601,10 @@
         <v>6</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -13692,7 +13636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -13724,7 +13668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -13753,10 +13697,10 @@
         <v>7</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -13788,7 +13732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -13820,7 +13764,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -13849,10 +13793,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -13881,10 +13825,10 @@
         <v>6</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>139</v>
       </c>
@@ -13916,7 +13860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -13948,7 +13892,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -13980,7 +13924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -14009,10 +13953,10 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -14044,7 +13988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -14076,7 +14020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -14108,7 +14052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -14140,7 +14084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -14169,10 +14113,10 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -14201,10 +14145,10 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -14236,7 +14180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -14265,10 +14209,10 @@
         <v>6</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -14300,7 +14244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -14332,7 +14276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -14364,7 +14308,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -14393,10 +14337,10 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>180</v>
       </c>
@@ -14425,10 +14369,10 @@
         <v>6</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -14460,7 +14404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -14492,7 +14436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -14521,10 +14465,10 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -14556,7 +14500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -14588,7 +14532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -14620,7 +14564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -14652,7 +14596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>174</v>
       </c>
@@ -14684,7 +14628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -14716,7 +14660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -14745,10 +14689,10 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -14777,10 +14721,10 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -14809,7 +14753,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -14818,14 +14762,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
-  <cols>
-    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14857,7 +14798,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -14886,7 +14827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -14915,10 +14856,10 @@
         <v>6</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -14950,7 +14891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -14979,10 +14920,10 @@
         <v>7</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -15014,7 +14955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -15046,7 +14987,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -15078,7 +15019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -15107,10 +15048,10 @@
         <v>6</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -15139,10 +15080,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -15171,10 +15112,10 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -15206,7 +15147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>95</v>
       </c>
@@ -15235,10 +15176,10 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -15270,7 +15211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -15302,7 +15243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -15334,7 +15275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -15366,7 +15307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -15395,10 +15336,10 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -15427,10 +15368,10 @@
         <v>6</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -15462,7 +15403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>100</v>
       </c>
@@ -15494,7 +15435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -15523,10 +15464,10 @@
         <v>6</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -15558,7 +15499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -15590,7 +15531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -15619,10 +15560,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -15651,10 +15592,10 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -15686,7 +15627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -15718,7 +15659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -15747,10 +15688,10 @@
         <v>6</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>104</v>
       </c>
@@ -15782,7 +15723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -15811,10 +15752,10 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -15846,7 +15787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -15875,10 +15816,10 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -15910,7 +15851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -15942,7 +15883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -15974,7 +15915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>109</v>
       </c>
@@ -16003,10 +15944,10 @@
         <v>5</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -16038,7 +15979,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -16076,11 +16017,11 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16112,7 +16053,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -16141,7 +16082,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -16173,7 +16114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -16205,7 +16146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -16234,10 +16175,10 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -16269,7 +16210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -16301,7 +16242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -16330,10 +16271,10 @@
         <v>6</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -16362,10 +16303,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>186</v>
       </c>
@@ -16397,7 +16338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -16426,10 +16367,10 @@
         <v>5</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -16458,10 +16399,10 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -16493,7 +16434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -16525,7 +16466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -16557,7 +16498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -16586,10 +16527,10 @@
         <v>7</v>
       </c>
       <c r="J16" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -16618,10 +16559,10 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -16653,7 +16594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -16685,7 +16626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -16714,10 +16655,10 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -16746,10 +16687,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -16781,7 +16722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>182</v>
       </c>
@@ -16813,7 +16754,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -16842,10 +16783,10 @@
         <v>5</v>
       </c>
       <c r="J24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -16874,10 +16815,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -16909,7 +16850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -16941,7 +16882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -16970,10 +16911,10 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -17002,10 +16943,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -17037,7 +16978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -17066,10 +17007,10 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -17101,7 +17042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -17130,10 +17071,10 @@
         <v>5</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -17165,7 +17106,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -17197,7 +17138,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -17229,7 +17170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>167</v>
       </c>
@@ -17258,10 +17199,10 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -17293,7 +17234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -17331,11 +17272,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17367,7 +17308,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -17396,7 +17337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -17428,7 +17369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -17460,7 +17401,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -17489,10 +17430,10 @@
         <v>7</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -17524,7 +17465,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -17556,7 +17497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -17585,10 +17526,10 @@
         <v>6</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -17617,10 +17558,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -17649,10 +17590,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -17681,10 +17622,10 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -17713,10 +17654,10 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>127</v>
       </c>
@@ -17748,7 +17689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -17780,7 +17721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>128</v>
       </c>
@@ -17812,7 +17753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -17844,7 +17785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -17873,10 +17814,10 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -17908,7 +17849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -17940,7 +17881,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -17972,7 +17913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -18001,10 +17942,10 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -18033,10 +17974,10 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -18068,7 +18009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -18100,7 +18041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -18129,10 +18070,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -18161,10 +18102,10 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -18193,10 +18134,10 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -18228,7 +18169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -18257,10 +18198,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -18289,10 +18230,10 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -18324,7 +18265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -18353,10 +18294,10 @@
         <v>7</v>
       </c>
       <c r="J32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -18388,7 +18329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -18420,7 +18361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -18452,7 +18393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -18484,7 +18425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -18516,7 +18457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -18548,7 +18489,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -18577,7 +18518,7 @@
         <v>5</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -18586,11 +18527,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -18622,7 +18563,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -18651,7 +18592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -18680,10 +18621,10 @@
         <v>6</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -18715,7 +18656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -18747,7 +18688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -18776,10 +18717,10 @@
         <v>7</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -18811,7 +18752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -18840,10 +18781,10 @@
         <v>5</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -18872,10 +18813,10 @@
         <v>5</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -18904,10 +18845,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>138</v>
       </c>
@@ -18939,7 +18880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>139</v>
       </c>
@@ -18968,10 +18909,10 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>93</v>
       </c>
@@ -19003,7 +18944,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -19032,10 +18973,10 @@
         <v>7</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>140</v>
       </c>
@@ -19064,10 +19005,10 @@
         <v>7</v>
       </c>
       <c r="J15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -19099,7 +19040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -19131,7 +19072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -19163,7 +19104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -19192,10 +19133,10 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -19224,10 +19165,10 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -19256,10 +19197,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -19288,10 +19229,10 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -19320,10 +19261,10 @@
         <v>7</v>
       </c>
       <c r="J23" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -19355,7 +19296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>141</v>
       </c>
@@ -19387,7 +19328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>132</v>
       </c>
@@ -19416,10 +19357,10 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -19448,10 +19389,10 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>133</v>
       </c>
@@ -19480,10 +19421,10 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>103</v>
       </c>
@@ -19515,7 +19456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>142</v>
       </c>
@@ -19544,10 +19485,10 @@
         <v>7</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -19579,7 +19520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -19611,7 +19552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -19643,7 +19584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -19672,10 +19613,10 @@
         <v>7</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -19707,7 +19648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -19739,7 +19680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -19771,7 +19712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -19803,7 +19744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -19841,11 +19782,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19877,7 +19818,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -19906,7 +19847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -19935,10 +19876,10 @@
         <v>6</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -19970,7 +19911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -20002,7 +19943,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -20031,10 +19972,10 @@
         <v>7</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -20066,7 +20007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -20098,7 +20039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -20127,10 +20068,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>147</v>
       </c>
@@ -20162,7 +20103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -20191,10 +20132,10 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -20223,10 +20164,10 @@
         <v>6</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -20258,7 +20199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -20290,7 +20231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -20322,7 +20263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -20354,7 +20295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -20383,10 +20324,10 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>148</v>
       </c>
@@ -20418,7 +20359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -20450,7 +20391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -20479,10 +20420,10 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -20511,10 +20452,10 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -20546,7 +20487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -20578,7 +20519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -20610,7 +20551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -20639,10 +20580,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -20671,10 +20612,10 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -20703,10 +20644,10 @@
         <v>7</v>
       </c>
       <c r="J27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -20738,7 +20679,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -20770,7 +20711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -20799,10 +20740,10 @@
         <v>6</v>
       </c>
       <c r="J30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -20834,7 +20775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -20866,7 +20807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -20898,7 +20839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -20930,7 +20871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -20962,7 +20903,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -20994,7 +20935,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -21026,7 +20967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>150</v>
       </c>
@@ -21058,7 +20999,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -21087,7 +21028,7 @@
         <v>7</v>
       </c>
       <c r="J39" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21096,11 +21037,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21132,7 +21073,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -21161,7 +21102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -21193,7 +21134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -21222,10 +21163,10 @@
         <v>5</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -21257,7 +21198,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -21286,10 +21227,10 @@
         <v>7</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -21321,7 +21262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -21353,7 +21294,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -21382,10 +21323,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -21414,10 +21355,10 @@
         <v>7</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -21446,10 +21387,10 @@
         <v>7</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -21478,10 +21419,10 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -21510,10 +21451,10 @@
         <v>7</v>
       </c>
       <c r="J13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>140</v>
       </c>
@@ -21542,10 +21483,10 @@
         <v>6</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -21577,7 +21518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -21609,7 +21550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -21641,7 +21582,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>129</v>
       </c>
@@ -21670,10 +21611,10 @@
         <v>7</v>
       </c>
       <c r="J18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -21702,10 +21643,10 @@
         <v>7</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -21734,10 +21675,10 @@
         <v>7</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -21766,10 +21707,10 @@
         <v>7</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -21798,10 +21739,10 @@
         <v>7</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -21833,7 +21774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>153</v>
       </c>
@@ -21865,7 +21806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -21897,7 +21838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -21926,10 +21867,10 @@
         <v>6</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>154</v>
       </c>
@@ -21961,7 +21902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -21990,10 +21931,10 @@
         <v>5</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -22022,10 +21963,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -22057,7 +21998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -22086,10 +22027,10 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -22121,7 +22062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -22150,10 +22091,10 @@
         <v>7</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -22185,7 +22126,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -22217,7 +22158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -22246,10 +22187,10 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -22278,10 +22219,10 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -22313,7 +22254,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -22351,11 +22292,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22387,7 +22328,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -22416,7 +22357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -22445,10 +22386,10 @@
         <v>5</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>157</v>
       </c>
@@ -22477,10 +22418,10 @@
         <v>6</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -22512,7 +22453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -22541,10 +22482,10 @@
         <v>7</v>
       </c>
       <c r="J6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -22576,7 +22517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -22608,7 +22549,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>158</v>
       </c>
@@ -22640,7 +22581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -22669,10 +22610,10 @@
         <v>5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -22704,7 +22645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>159</v>
       </c>
@@ -22736,7 +22677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -22768,7 +22709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>160</v>
       </c>
@@ -22797,10 +22738,10 @@
         <v>5</v>
       </c>
       <c r="J14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -22832,7 +22773,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>162</v>
       </c>
@@ -22864,7 +22805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -22896,7 +22837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -22928,7 +22869,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>163</v>
       </c>
@@ -22957,10 +22898,10 @@
         <v>5</v>
       </c>
       <c r="J19" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -22992,7 +22933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -23021,10 +22962,10 @@
         <v>6</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -23056,7 +22997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -23088,7 +23029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>141</v>
       </c>
@@ -23120,7 +23061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -23149,10 +23090,10 @@
         <v>7</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>164</v>
       </c>
@@ -23181,10 +23122,10 @@
         <v>5</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -23216,7 +23157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -23248,7 +23189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -23277,10 +23218,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>165</v>
       </c>
@@ -23312,7 +23253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -23341,10 +23282,10 @@
         <v>6</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -23376,7 +23317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -23408,7 +23349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -23440,7 +23381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -23472,7 +23413,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -23501,10 +23442,10 @@
         <v>6</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>167</v>
       </c>
@@ -23536,7 +23477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -23568,7 +23509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -23606,11 +23547,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -23642,7 +23583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -23671,7 +23612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -23703,7 +23644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -23735,7 +23676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -23764,10 +23705,10 @@
         <v>6</v>
       </c>
       <c r="J5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -23799,7 +23740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -23831,7 +23772,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -23863,7 +23804,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>170</v>
       </c>
@@ -23892,10 +23833,10 @@
         <v>7</v>
       </c>
       <c r="J9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -23924,10 +23865,10 @@
         <v>5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -23956,10 +23897,10 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -23988,10 +23929,10 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -24023,7 +23964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -24055,7 +23996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -24087,7 +24028,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -24119,7 +24060,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -24148,10 +24089,10 @@
         <v>7</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -24183,7 +24124,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -24215,7 +24156,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>171</v>
       </c>
@@ -24247,7 +24188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -24276,10 +24217,10 @@
         <v>5</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -24311,7 +24252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -24343,7 +24284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -24375,7 +24316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -24404,10 +24345,10 @@
         <v>5</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -24439,7 +24380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -24471,7 +24412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -24500,10 +24441,10 @@
         <v>7</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -24532,10 +24473,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -24567,7 +24508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -24596,10 +24537,10 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -24631,7 +24572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -24663,7 +24604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -24695,7 +24636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -24727,7 +24668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -24756,10 +24697,10 @@
         <v>7</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>150</v>
       </c>
@@ -24788,10 +24729,10 @@
         <v>5</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -24820,10 +24761,10 @@
         <v>6</v>
       </c>
       <c r="J38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -24861,11 +24802,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24897,7 +24838,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -24926,7 +24867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -24955,10 +24896,10 @@
         <v>7</v>
       </c>
       <c r="J3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -24987,10 +24928,10 @@
         <v>7</v>
       </c>
       <c r="J4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -25022,7 +24963,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -25054,7 +24995,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -25086,7 +25027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -25115,10 +25056,10 @@
         <v>7</v>
       </c>
       <c r="J8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>170</v>
       </c>
@@ -25150,7 +25091,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -25179,10 +25120,10 @@
         <v>5</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -25211,10 +25152,10 @@
         <v>6</v>
       </c>
       <c r="J11" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -25243,10 +25184,10 @@
         <v>7</v>
       </c>
       <c r="J12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -25278,7 +25219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -25310,7 +25251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -25342,7 +25283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>162</v>
       </c>
@@ -25374,7 +25315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -25403,10 +25344,10 @@
         <v>6</v>
       </c>
       <c r="J17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -25438,7 +25379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -25470,7 +25411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>173</v>
       </c>
@@ -25499,10 +25440,10 @@
         <v>6</v>
       </c>
       <c r="J20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -25534,7 +25475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -25566,7 +25507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -25598,7 +25539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -25630,7 +25571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -25659,10 +25600,10 @@
         <v>6</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -25691,10 +25632,10 @@
         <v>7</v>
       </c>
       <c r="J26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -25726,7 +25667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -25755,10 +25696,10 @@
         <v>6</v>
       </c>
       <c r="J28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -25787,10 +25728,10 @@
         <v>7</v>
       </c>
       <c r="J29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -25822,7 +25763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -25851,10 +25792,10 @@
         <v>7</v>
       </c>
       <c r="J31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -25886,7 +25827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -25915,10 +25856,10 @@
         <v>6</v>
       </c>
       <c r="J33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>174</v>
       </c>
@@ -25947,10 +25888,10 @@
         <v>5</v>
       </c>
       <c r="J34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -25982,7 +25923,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -26011,10 +25952,10 @@
         <v>6</v>
       </c>
       <c r="J36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -26043,10 +25984,10 @@
         <v>7</v>
       </c>
       <c r="J37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -26078,7 +26019,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>111</v>
       </c>

--- a/23:24/PLteamsData23:24_with_tight_schedule.xlsx
+++ b/23:24/PLteamsData23:24_with_tight_schedule.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="11211"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shlomiasraf/Desktop/degree/MomentumProject/23:24/PLteamsData23:"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D7CA090-E315-284D-B9C3-F53B02B8B59B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="760" windowWidth="21620" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Arsenal" sheetId="1" r:id="rId1"/>
@@ -28,7 +34,7 @@
     <sheet name="West Ham" sheetId="19" r:id="rId19"/>
     <sheet name="Wolves" sheetId="20" r:id="rId20"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -602,15 +608,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -618,7 +624,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -670,11 +676,19 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="ערכת נושא Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -716,7 +730,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -748,9 +762,27 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -782,6 +814,24 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -957,11 +1007,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -993,7 +1043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1018,11 +1068,14 @@
       <c r="H2" s="2">
         <v>44934</v>
       </c>
+      <c r="I2">
+        <v>8</v>
+      </c>
       <c r="J2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1054,7 +1107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -1086,7 +1139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -1118,7 +1171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -1150,7 +1203,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -1182,7 +1235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -1214,7 +1267,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -1246,7 +1299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1278,7 +1331,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1310,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -1342,7 +1395,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>21</v>
       </c>
@@ -1374,7 +1427,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>22</v>
       </c>
@@ -1406,7 +1459,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -1438,7 +1491,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1470,7 +1523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -1502,7 +1555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>26</v>
       </c>
@@ -1534,7 +1587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1566,7 +1619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -1598,7 +1651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>29</v>
       </c>
@@ -1630,7 +1683,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -1662,7 +1715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -1694,7 +1747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -1726,7 +1779,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -1758,7 +1811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -1790,7 +1843,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -1822,7 +1875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -1854,7 +1907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -1886,7 +1939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -1918,7 +1971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -1950,7 +2003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -1982,7 +2035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -2014,7 +2067,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -2046,7 +2099,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -2078,7 +2131,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -2110,7 +2163,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -2142,7 +2195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -2174,7 +2227,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -2212,11 +2265,11 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2248,7 +2301,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -2277,7 +2330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -2309,7 +2362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>157</v>
       </c>
@@ -2341,7 +2394,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>176</v>
       </c>
@@ -2373,7 +2426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -2405,7 +2458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2437,7 +2490,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -2469,7 +2522,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -2501,7 +2554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2533,7 +2586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -2565,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -2597,7 +2650,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2629,7 +2682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>140</v>
       </c>
@@ -2661,7 +2714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -2693,7 +2746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -2725,7 +2778,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -2757,7 +2810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -2789,7 +2842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -2821,7 +2874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -2853,7 +2906,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -2885,7 +2938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -2917,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -2949,7 +3002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -2981,7 +3034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -3013,7 +3066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3045,7 +3098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -3077,7 +3130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -3109,7 +3162,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -3141,7 +3194,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -3173,7 +3226,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -3205,7 +3258,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -3237,7 +3290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -3269,7 +3322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -3301,7 +3354,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -3333,7 +3386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -3365,7 +3418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -3397,7 +3450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -3429,7 +3482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -3467,11 +3520,11 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3503,7 +3556,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -3532,7 +3585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3564,7 +3617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -3596,7 +3649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3628,7 +3681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -3660,7 +3713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -3692,7 +3745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3724,7 +3777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -3756,7 +3809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3788,7 +3841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>179</v>
       </c>
@@ -3820,7 +3873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -3852,7 +3905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -3884,7 +3937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3916,7 +3969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>160</v>
       </c>
@@ -3948,7 +4001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>161</v>
       </c>
@@ -3980,7 +4033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4012,7 +4065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -4044,7 +4097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -4076,7 +4129,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -4108,7 +4161,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -4140,7 +4193,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>100</v>
       </c>
@@ -4172,7 +4225,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -4204,7 +4257,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>141</v>
       </c>
@@ -4236,7 +4289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -4268,7 +4321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -4300,7 +4353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>34</v>
       </c>
@@ -4332,7 +4385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -4364,7 +4417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -4396,7 +4449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -4428,7 +4481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -4460,7 +4513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -4492,7 +4545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -4524,7 +4577,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -4556,7 +4609,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -4588,7 +4641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -4620,7 +4673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -4652,7 +4705,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -4684,7 +4737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -4722,11 +4775,11 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4758,7 +4811,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -4787,7 +4840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -4819,7 +4872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -4851,7 +4904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4883,7 +4936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -4915,7 +4968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4947,7 +5000,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -4979,7 +5032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -5011,7 +5064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>147</v>
       </c>
@@ -5043,7 +5096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>179</v>
       </c>
@@ -5075,7 +5128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -5107,7 +5160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -5139,7 +5192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>127</v>
       </c>
@@ -5171,7 +5224,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>140</v>
       </c>
@@ -5203,7 +5256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -5235,7 +5288,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -5267,7 +5320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -5299,7 +5352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -5331,7 +5384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -5363,7 +5416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -5395,7 +5448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>173</v>
       </c>
@@ -5427,7 +5480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -5459,7 +5512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -5491,7 +5544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>31</v>
       </c>
@@ -5523,7 +5576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>164</v>
       </c>
@@ -5555,7 +5608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>180</v>
       </c>
@@ -5587,7 +5640,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -5619,7 +5672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -5651,7 +5704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -5683,7 +5736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -5715,7 +5768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -5747,7 +5800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -5779,7 +5832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -5811,7 +5864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>42</v>
       </c>
@@ -5843,7 +5896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -5875,7 +5928,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -5907,7 +5960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -5939,7 +5992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -5977,11 +6030,11 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6013,7 +6066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -6042,7 +6095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>157</v>
       </c>
@@ -6074,7 +6127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -6106,7 +6159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -6138,7 +6191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -6170,7 +6223,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -6202,7 +6255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -6234,7 +6287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -6266,7 +6319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>138</v>
       </c>
@@ -6298,7 +6351,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6330,7 +6383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -6362,7 +6415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -6394,7 +6447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -6426,7 +6479,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -6458,7 +6511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -6490,7 +6543,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -6522,7 +6575,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>148</v>
       </c>
@@ -6554,7 +6607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -6586,7 +6639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -6618,7 +6671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -6650,7 +6703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>181</v>
       </c>
@@ -6682,7 +6735,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -6714,7 +6767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>153</v>
       </c>
@@ -6746,7 +6799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -6778,7 +6831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -6810,7 +6863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -6842,7 +6895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -6874,7 +6927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -6906,7 +6959,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -6938,7 +6991,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -6970,7 +7023,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -7002,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -7034,7 +7087,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -7066,7 +7119,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -7098,7 +7151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -7130,7 +7183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>155</v>
       </c>
@@ -7162,7 +7215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -7194,7 +7247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -7232,11 +7285,11 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -7268,7 +7321,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -7297,7 +7350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -7329,7 +7382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -7361,7 +7414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -7393,7 +7446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -7425,7 +7478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -7457,7 +7510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -7489,7 +7542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -7521,7 +7574,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -7553,7 +7606,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -7585,7 +7638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -7617,7 +7670,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -7649,7 +7702,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>160</v>
       </c>
@@ -7681,7 +7734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -7713,7 +7766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -7745,7 +7798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>130</v>
       </c>
@@ -7777,7 +7830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -7809,7 +7862,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>171</v>
       </c>
@@ -7841,7 +7894,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -7873,7 +7926,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>149</v>
       </c>
@@ -7905,7 +7958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -7937,7 +7990,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>182</v>
       </c>
@@ -7969,7 +8022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -8001,7 +8054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -8033,7 +8086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -8065,7 +8118,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -8097,7 +8150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -8129,7 +8182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -8161,7 +8214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -8193,7 +8246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -8225,7 +8278,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -8257,7 +8310,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -8289,7 +8342,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -8321,7 +8374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -8353,7 +8406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -8385,7 +8438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -8417,7 +8470,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -8449,7 +8502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -8487,11 +8540,11 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0E00-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8523,7 +8576,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -8552,7 +8605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -8584,7 +8637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>157</v>
       </c>
@@ -8616,7 +8669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -8648,7 +8701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -8680,7 +8733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -8712,7 +8765,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -8744,7 +8797,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -8776,7 +8829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -8808,7 +8861,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -8840,7 +8893,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -8872,7 +8925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>159</v>
       </c>
@@ -8904,7 +8957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -8936,7 +8989,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>128</v>
       </c>
@@ -8968,7 +9021,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -9000,7 +9053,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -9032,7 +9085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -9064,7 +9117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -9096,7 +9149,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -9128,7 +9181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -9160,7 +9213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -9192,7 +9245,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -9224,7 +9277,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -9256,7 +9309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -9288,7 +9341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>102</v>
       </c>
@@ -9320,7 +9373,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -9352,7 +9405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -9384,7 +9437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -9416,7 +9469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -9448,7 +9501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -9480,7 +9533,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -9512,7 +9565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -9544,7 +9597,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -9576,7 +9629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>174</v>
       </c>
@@ -9608,7 +9661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -9640,7 +9693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>155</v>
       </c>
@@ -9672,7 +9725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -9704,7 +9757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>110</v>
       </c>
@@ -9742,11 +9795,11 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -9778,7 +9831,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -9807,7 +9860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -9839,7 +9892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -9871,7 +9924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -9903,7 +9956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -9935,7 +9988,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -9967,7 +10020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -9999,7 +10052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -10031,7 +10084,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -10063,7 +10116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -10095,7 +10148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -10127,7 +10180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -10159,7 +10212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>140</v>
       </c>
@@ -10191,7 +10244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -10223,7 +10276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -10255,7 +10308,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>161</v>
       </c>
@@ -10287,7 +10340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>129</v>
       </c>
@@ -10319,7 +10372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -10351,7 +10404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -10383,7 +10436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -10415,7 +10468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -10447,7 +10500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -10479,7 +10532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -10511,7 +10564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>184</v>
       </c>
@@ -10543,7 +10596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -10575,7 +10628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -10607,7 +10660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>154</v>
       </c>
@@ -10639,7 +10692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>142</v>
       </c>
@@ -10671,7 +10724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>104</v>
       </c>
@@ -10703,7 +10756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -10735,7 +10788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -10767,7 +10820,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -10799,7 +10852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -10831,7 +10884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -10863,7 +10916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -10895,7 +10948,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -10927,7 +10980,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -10959,7 +11012,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -10997,11 +11050,11 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1000-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11033,7 +11086,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -11062,7 +11115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -11094,7 +11147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -11126,7 +11179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -11158,7 +11211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -11190,7 +11243,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -11222,7 +11275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -11254,7 +11307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>147</v>
       </c>
@@ -11286,7 +11339,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>186</v>
       </c>
@@ -11318,7 +11371,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -11350,7 +11403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -11382,7 +11435,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -11414,7 +11467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>160</v>
       </c>
@@ -11446,7 +11499,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -11478,7 +11531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -11510,7 +11563,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -11542,7 +11595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -11574,7 +11627,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -11606,7 +11659,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -11638,7 +11691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -11670,7 +11723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -11702,7 +11755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -11734,7 +11787,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>184</v>
       </c>
@@ -11766,7 +11819,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -11798,7 +11851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -11830,7 +11883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -11862,7 +11915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -11894,7 +11947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -11926,7 +11979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -11958,7 +12011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -11990,7 +12043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -12022,7 +12075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -12054,7 +12107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -12086,7 +12139,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -12118,7 +12171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -12150,7 +12203,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>109</v>
       </c>
@@ -12182,7 +12235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -12214,7 +12267,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -12252,11 +12305,11 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1100-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -12288,7 +12341,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -12317,7 +12370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -12349,7 +12402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>176</v>
       </c>
@@ -12381,7 +12434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -12413,7 +12466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>136</v>
       </c>
@@ -12445,7 +12498,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -12477,7 +12530,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -12509,7 +12562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -12541,7 +12594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>93</v>
       </c>
@@ -12573,7 +12626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>94</v>
       </c>
@@ -12605,7 +12658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>140</v>
       </c>
@@ -12637,7 +12690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -12669,7 +12722,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -12701,7 +12754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -12733,7 +12786,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -12765,7 +12818,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>27</v>
       </c>
@@ -12797,7 +12850,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>163</v>
       </c>
@@ -12829,7 +12882,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>99</v>
       </c>
@@ -12861,7 +12914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>131</v>
       </c>
@@ -12893,7 +12946,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>181</v>
       </c>
@@ -12925,7 +12978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -12957,7 +13010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>141</v>
       </c>
@@ -12989,7 +13042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -13021,7 +13074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -13053,7 +13106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -13085,7 +13138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -13117,7 +13170,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -13149,7 +13202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -13181,7 +13234,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>165</v>
       </c>
@@ -13213,7 +13266,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -13245,7 +13298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -13277,7 +13330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -13309,7 +13362,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>174</v>
       </c>
@@ -13341,7 +13394,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -13373,7 +13426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>185</v>
       </c>
@@ -13405,7 +13458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -13437,7 +13490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>46</v>
       </c>
@@ -13469,7 +13522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -13507,11 +13560,11 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13543,7 +13596,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -13572,7 +13625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -13604,7 +13657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -13636,7 +13689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -13668,7 +13721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -13700,7 +13753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>124</v>
       </c>
@@ -13732,7 +13785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -13764,7 +13817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -13796,7 +13849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -13828,7 +13881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>139</v>
       </c>
@@ -13860,7 +13913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -13892,7 +13945,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -13924,7 +13977,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>95</v>
       </c>
@@ -13956,7 +14009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -13988,7 +14041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -14020,7 +14073,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -14052,7 +14105,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>24</v>
       </c>
@@ -14084,7 +14137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>97</v>
       </c>
@@ -14116,7 +14169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -14148,7 +14201,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>99</v>
       </c>
@@ -14180,7 +14233,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -14212,7 +14265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -14244,7 +14297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -14276,7 +14329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -14308,7 +14361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -14340,7 +14393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>180</v>
       </c>
@@ -14372,7 +14425,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -14404,7 +14457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -14436,7 +14489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -14468,7 +14521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -14500,7 +14553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -14532,7 +14585,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -14564,7 +14617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -14596,7 +14649,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>174</v>
       </c>
@@ -14628,7 +14681,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>166</v>
       </c>
@@ -14660,7 +14713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -14692,7 +14745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>45</v>
       </c>
@@ -14724,7 +14777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -14762,11 +14815,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14798,7 +14851,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -14827,7 +14880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -14859,7 +14912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -14891,7 +14944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -14923,7 +14976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -14955,7 +15008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -14987,7 +15040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -15019,7 +15072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -15051,7 +15104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -15083,7 +15136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -15115,7 +15168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -15147,7 +15200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>95</v>
       </c>
@@ -15179,7 +15232,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -15211,7 +15264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -15243,7 +15296,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -15275,7 +15328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -15307,7 +15360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -15339,7 +15392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -15371,7 +15424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -15403,7 +15456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>100</v>
       </c>
@@ -15435,7 +15488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -15467,7 +15520,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -15499,7 +15552,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -15531,7 +15584,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -15563,7 +15616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -15595,7 +15648,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -15627,7 +15680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>36</v>
       </c>
@@ -15659,7 +15712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -15691,7 +15744,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>104</v>
       </c>
@@ -15723,7 +15776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -15755,7 +15808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -15787,7 +15840,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -15819,7 +15872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -15851,7 +15904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -15883,7 +15936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -15915,7 +15968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>109</v>
       </c>
@@ -15947,7 +16000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -15979,7 +16032,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -16017,11 +16070,11 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1300-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -16053,7 +16106,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -16082,7 +16135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -16114,7 +16167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>90</v>
       </c>
@@ -16146,7 +16199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -16178,7 +16231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -16210,7 +16263,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -16242,7 +16295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -16274,7 +16327,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -16306,7 +16359,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>186</v>
       </c>
@@ -16338,7 +16391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -16370,7 +16423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -16402,7 +16455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -16434,7 +16487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -16466,7 +16519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -16498,7 +16551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>129</v>
       </c>
@@ -16530,7 +16583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>25</v>
       </c>
@@ -16562,7 +16615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -16594,7 +16647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -16626,7 +16679,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>28</v>
       </c>
@@ -16658,7 +16711,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -16690,7 +16743,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -16722,7 +16775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>182</v>
       </c>
@@ -16754,7 +16807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -16786,7 +16839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -16818,7 +16871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -16850,7 +16903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -16882,7 +16935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -16914,7 +16967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -16946,7 +16999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -16978,7 +17031,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -17010,7 +17063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>177</v>
       </c>
@@ -17042,7 +17095,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -17074,7 +17127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -17106,7 +17159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -17138,7 +17191,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>44</v>
       </c>
@@ -17170,7 +17223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>167</v>
       </c>
@@ -17202,7 +17255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -17234,7 +17287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -17272,11 +17325,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -17308,7 +17361,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -17337,7 +17390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -17369,7 +17422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -17401,7 +17454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -17433,7 +17486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>124</v>
       </c>
@@ -17465,7 +17518,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -17497,7 +17550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -17529,7 +17582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>17</v>
       </c>
@@ -17561,7 +17614,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -17593,7 +17646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>126</v>
       </c>
@@ -17625,7 +17678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -17657,7 +17710,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>127</v>
       </c>
@@ -17689,7 +17742,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>96</v>
       </c>
@@ -17721,7 +17774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>128</v>
       </c>
@@ -17753,7 +17806,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -17785,7 +17838,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -17817,7 +17870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>97</v>
       </c>
@@ -17849,7 +17902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>130</v>
       </c>
@@ -17881,7 +17934,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -17913,7 +17966,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -17945,7 +17998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -17977,7 +18030,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -18009,7 +18062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -18041,7 +18094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -18073,7 +18126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -18105,7 +18158,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -18137,7 +18190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -18169,7 +18222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -18201,7 +18254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -18233,7 +18286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -18265,7 +18318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>39</v>
       </c>
@@ -18297,7 +18350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -18329,7 +18382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -18361,7 +18414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -18393,7 +18446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -18425,7 +18478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -18457,7 +18510,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -18489,7 +18542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>47</v>
       </c>
@@ -18527,11 +18580,11 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -18563,7 +18616,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>135</v>
       </c>
@@ -18592,7 +18645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -18624,7 +18677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -18656,7 +18709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -18688,7 +18741,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -18720,7 +18773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -18752,7 +18805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>137</v>
       </c>
@@ -18784,7 +18837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -18816,7 +18869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -18848,7 +18901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>138</v>
       </c>
@@ -18880,7 +18933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>139</v>
       </c>
@@ -18912,7 +18965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>93</v>
       </c>
@@ -18944,7 +18997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -18976,7 +19029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>140</v>
       </c>
@@ -19008,7 +19061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>96</v>
       </c>
@@ -19040,7 +19093,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>22</v>
       </c>
@@ -19072,7 +19125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -19104,7 +19157,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>129</v>
       </c>
@@ -19136,7 +19189,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -19168,7 +19221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>98</v>
       </c>
@@ -19200,7 +19253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>28</v>
       </c>
@@ -19232,7 +19285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>131</v>
       </c>
@@ -19264,7 +19317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>30</v>
       </c>
@@ -19296,7 +19349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>141</v>
       </c>
@@ -19328,7 +19381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>132</v>
       </c>
@@ -19360,7 +19413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>33</v>
       </c>
@@ -19392,7 +19445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>133</v>
       </c>
@@ -19424,7 +19477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>103</v>
       </c>
@@ -19456,7 +19509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>142</v>
       </c>
@@ -19488,7 +19541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -19520,7 +19573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -19552,7 +19605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -19584,7 +19637,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>41</v>
       </c>
@@ -19616,7 +19669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -19648,7 +19701,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -19680,7 +19733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -19712,7 +19765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -19744,7 +19797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -19782,11 +19835,11 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -19818,7 +19871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -19847,7 +19900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -19879,7 +19932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -19911,7 +19964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>90</v>
       </c>
@@ -19943,7 +19996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>91</v>
       </c>
@@ -19975,7 +20028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -20007,7 +20060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -20039,7 +20092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -20071,7 +20124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>147</v>
       </c>
@@ -20103,7 +20156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -20135,7 +20188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>93</v>
       </c>
@@ -20167,7 +20220,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -20199,7 +20252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -20231,7 +20284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -20263,7 +20316,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -20295,7 +20348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>129</v>
       </c>
@@ -20327,7 +20380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>148</v>
       </c>
@@ -20359,7 +20412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -20391,7 +20444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -20423,7 +20476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -20455,7 +20508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -20487,7 +20540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -20519,7 +20572,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -20551,7 +20604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>132</v>
       </c>
@@ -20583,7 +20636,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -20615,7 +20668,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -20647,7 +20700,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>103</v>
       </c>
@@ -20679,7 +20732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -20711,7 +20764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>37</v>
       </c>
@@ -20743,7 +20796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>38</v>
       </c>
@@ -20775,7 +20828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>105</v>
       </c>
@@ -20807,7 +20860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -20839,7 +20892,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>107</v>
       </c>
@@ -20871,7 +20924,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>108</v>
       </c>
@@ -20903,7 +20956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>43</v>
       </c>
@@ -20935,7 +20988,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>44</v>
       </c>
@@ -20967,7 +21020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>150</v>
       </c>
@@ -20999,7 +21052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>46</v>
       </c>
@@ -21037,11 +21090,11 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -21073,7 +21126,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>151</v>
       </c>
@@ -21102,7 +21155,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -21134,7 +21187,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>152</v>
       </c>
@@ -21166,7 +21219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -21198,7 +21251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -21230,7 +21283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -21262,7 +21315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>92</v>
       </c>
@@ -21294,7 +21347,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>125</v>
       </c>
@@ -21326,7 +21379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -21358,7 +21411,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -21390,7 +21443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>126</v>
       </c>
@@ -21422,7 +21475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>94</v>
       </c>
@@ -21454,7 +21507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>140</v>
       </c>
@@ -21486,7 +21539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>96</v>
       </c>
@@ -21518,7 +21571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>128</v>
       </c>
@@ -21550,7 +21603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -21582,7 +21635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>129</v>
       </c>
@@ -21614,7 +21667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -21646,7 +21699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>98</v>
       </c>
@@ -21678,7 +21731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -21710,7 +21763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>131</v>
       </c>
@@ -21742,7 +21795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -21774,7 +21827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>153</v>
       </c>
@@ -21806,7 +21859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>102</v>
       </c>
@@ -21838,7 +21891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -21870,7 +21923,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>154</v>
       </c>
@@ -21902,7 +21955,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -21934,7 +21987,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -21966,7 +22019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -21998,7 +22051,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -22030,7 +22083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -22062,7 +22115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -22094,7 +22147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>42</v>
       </c>
@@ -22126,7 +22179,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -22158,7 +22211,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -22190,7 +22243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -22222,7 +22275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>110</v>
       </c>
@@ -22254,7 +22307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -22292,11 +22345,11 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -22328,7 +22381,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>146</v>
       </c>
@@ -22357,7 +22410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>123</v>
       </c>
@@ -22389,7 +22442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>157</v>
       </c>
@@ -22421,7 +22474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -22453,7 +22506,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -22485,7 +22538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>136</v>
       </c>
@@ -22517,7 +22570,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -22549,7 +22602,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>158</v>
       </c>
@@ -22581,7 +22634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -22613,7 +22666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -22645,7 +22698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>159</v>
       </c>
@@ -22677,7 +22730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -22709,7 +22762,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>160</v>
       </c>
@@ -22741,7 +22794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>161</v>
       </c>
@@ -22773,7 +22826,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>162</v>
       </c>
@@ -22805,7 +22858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -22837,7 +22890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>98</v>
       </c>
@@ -22869,7 +22922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>163</v>
       </c>
@@ -22901,7 +22954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>99</v>
       </c>
@@ -22933,7 +22986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -22965,7 +23018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>149</v>
       </c>
@@ -22997,7 +23050,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -23029,7 +23082,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>141</v>
       </c>
@@ -23061,7 +23114,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>101</v>
       </c>
@@ -23093,7 +23146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>164</v>
       </c>
@@ -23125,7 +23178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>133</v>
       </c>
@@ -23157,7 +23210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>35</v>
       </c>
@@ -23189,7 +23242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>36</v>
       </c>
@@ -23221,7 +23274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>165</v>
       </c>
@@ -23253,7 +23306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>105</v>
       </c>
@@ -23285,7 +23338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -23317,7 +23370,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -23349,7 +23402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -23381,7 +23434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -23413,7 +23466,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -23445,7 +23498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>167</v>
       </c>
@@ -23477,7 +23530,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -23509,7 +23562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -23547,11 +23600,11 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -23583,7 +23636,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -23612,7 +23665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -23644,7 +23697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -23676,7 +23729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>169</v>
       </c>
@@ -23708,7 +23761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -23740,7 +23793,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -23772,7 +23825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>158</v>
       </c>
@@ -23804,7 +23857,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>170</v>
       </c>
@@ -23836,7 +23889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -23868,7 +23921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -23900,7 +23953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -23932,7 +23985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -23964,7 +24017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -23996,7 +24049,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -24028,7 +24081,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -24060,7 +24113,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -24092,7 +24145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -24124,7 +24177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -24156,7 +24209,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>171</v>
       </c>
@@ -24188,7 +24241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -24220,7 +24273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -24252,7 +24305,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -24284,7 +24337,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>32</v>
       </c>
@@ -24316,7 +24369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -24348,7 +24401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>34</v>
       </c>
@@ -24380,7 +24433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>103</v>
       </c>
@@ -24412,7 +24465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -24444,7 +24497,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -24476,7 +24529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -24508,7 +24561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -24540,7 +24593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -24572,7 +24625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>107</v>
       </c>
@@ -24604,7 +24657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>108</v>
       </c>
@@ -24636,7 +24689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>43</v>
       </c>
@@ -24668,7 +24721,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -24700,7 +24753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>150</v>
       </c>
@@ -24732,7 +24785,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -24764,7 +24817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
@@ -24802,11 +24855,11 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -24838,7 +24891,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
         <v>123</v>
       </c>
@@ -24867,7 +24920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
         <v>89</v>
       </c>
@@ -24899,7 +24952,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -24931,7 +24984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
         <v>91</v>
       </c>
@@ -24963,7 +25016,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -24995,7 +25048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
         <v>92</v>
       </c>
@@ -25027,7 +25080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
         <v>125</v>
       </c>
@@ -25059,7 +25112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
         <v>170</v>
       </c>
@@ -25091,7 +25144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -25123,7 +25176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A11" t="s">
         <v>93</v>
       </c>
@@ -25155,7 +25208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
         <v>20</v>
       </c>
@@ -25187,7 +25240,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A13" t="s">
         <v>96</v>
       </c>
@@ -25219,7 +25272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A14" t="s">
         <v>128</v>
       </c>
@@ -25251,7 +25304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A15" t="s">
         <v>23</v>
       </c>
@@ -25283,7 +25336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A16" t="s">
         <v>162</v>
       </c>
@@ -25315,7 +25368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A17" t="s">
         <v>97</v>
       </c>
@@ -25347,7 +25400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A18" t="s">
         <v>130</v>
       </c>
@@ -25379,7 +25432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A19" t="s">
         <v>98</v>
       </c>
@@ -25411,7 +25464,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A20" t="s">
         <v>173</v>
       </c>
@@ -25443,7 +25496,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A21" t="s">
         <v>131</v>
       </c>
@@ -25475,7 +25528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A22" t="s">
         <v>30</v>
       </c>
@@ -25507,7 +25560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A23" t="s">
         <v>31</v>
       </c>
@@ -25539,7 +25592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -25571,7 +25624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A25" t="s">
         <v>33</v>
       </c>
@@ -25603,7 +25656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A26" t="s">
         <v>133</v>
       </c>
@@ -25635,7 +25688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A27" t="s">
         <v>35</v>
       </c>
@@ -25667,7 +25720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A28" t="s">
         <v>142</v>
       </c>
@@ -25699,7 +25752,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A29" t="s">
         <v>37</v>
       </c>
@@ -25731,7 +25784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A30" t="s">
         <v>38</v>
       </c>
@@ -25763,7 +25816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A31" t="s">
         <v>39</v>
       </c>
@@ -25795,7 +25848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A32" t="s">
         <v>106</v>
       </c>
@@ -25827,7 +25880,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A33" t="s">
         <v>41</v>
       </c>
@@ -25859,7 +25912,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A34" t="s">
         <v>174</v>
       </c>
@@ -25891,7 +25944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A35" t="s">
         <v>166</v>
       </c>
@@ -25923,7 +25976,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -25955,7 +26008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A37" t="s">
         <v>45</v>
       </c>
@@ -25987,7 +26040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A38" t="s">
         <v>143</v>
       </c>
@@ -26019,7 +26072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.15">
       <c r="A39" t="s">
         <v>111</v>
       </c>
